--- a/AAII_Financials/Yearly/KPTI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KPTI_YR_FIN.xlsx
@@ -783,16 +783,16 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>131600</v>
+        <v>5900</v>
       </c>
       <c r="E9" s="3">
-        <v>149200</v>
+        <v>6000</v>
       </c>
       <c r="F9" s="3">
-        <v>143700</v>
+        <v>4900</v>
       </c>
       <c r="G9" s="3">
-        <v>153900</v>
+        <v>5200</v>
       </c>
       <c r="H9" s="3">
         <v>3400</v>
@@ -834,16 +834,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>14500</v>
+        <v>140100</v>
       </c>
       <c r="E10" s="3">
-        <v>-4000</v>
+        <v>139200</v>
       </c>
       <c r="F10" s="3">
-        <v>2300</v>
+        <v>141100</v>
       </c>
       <c r="G10" s="3">
-        <v>3200</v>
+        <v>151900</v>
       </c>
       <c r="H10" s="3">
         <v>206400</v>
